--- a/Bibsam_tidskriftslistor/scifree_data_markallen.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_markallen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_0A8D1EA792B46817A111619D6706502DC328179D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FCF2224-EDBD-4031-BB51-D4143124ECDD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06569E38-7459-49AA-8774-1B06A3D93D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="71">
   <si>
     <t>ISSN Electronic</t>
   </si>
@@ -61,9 +61,6 @@
     <t>British Journal of Nursing</t>
   </si>
   <si>
-    <t>British Journal of School Nursing</t>
-  </si>
-  <si>
     <t>Gastrointestinal Nursing</t>
   </si>
   <si>
@@ -106,9 +103,6 @@
     <t>2052-2819</t>
   </si>
   <si>
-    <t>2052-2827</t>
-  </si>
-  <si>
     <t>2052-2835</t>
   </si>
   <si>
@@ -190,18 +184,12 @@
     <t>https://www.magonlinelibrary.com/journal/ijtr</t>
   </si>
   <si>
-    <t>https://www.magonlinelibrary.com/loi/bjsn</t>
-  </si>
-  <si>
     <t>Dental Nursing</t>
   </si>
   <si>
     <t>1759-7404</t>
   </si>
   <si>
-    <t>https://www.markallengroup.com/brands/dental-nursing/</t>
-  </si>
-  <si>
     <t>2753-5932</t>
   </si>
   <si>
@@ -224,6 +212,27 @@
   </si>
   <si>
     <t>https://www.magonlinelibrary.com/journal/jfch</t>
+  </si>
+  <si>
+    <t>https://www.magonlinelibrary.com/journal/denn</t>
+  </si>
+  <si>
+    <t>2052-2878</t>
+  </si>
+  <si>
+    <t>Journal of Aesthetic Nursing</t>
+  </si>
+  <si>
+    <t>https://www.magonlinelibrary.com/journal/joan</t>
+  </si>
+  <si>
+    <t>2978-1523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Lower Limb Wound Care </t>
+  </si>
+  <si>
+    <t>https://www.magonlinelibrary.com/journal/llwc</t>
   </si>
 </sst>
 </file>
@@ -279,19 +288,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EF5B1489-08A2-44C7-9FF8-2BD2D67B8614}" name="Table1" displayName="Table1" ref="A1:G20" totalsRowShown="0">
-  <autoFilter ref="A1:G20" xr:uid="{EF5B1489-08A2-44C7-9FF8-2BD2D67B8614}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G20">
-    <sortCondition ref="D1:D20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{49E04D57-5B6F-47EC-961C-ED099BD000E4}" name="Table2" displayName="Table2" ref="A1:G21" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{49E04D57-5B6F-47EC-961C-ED099BD000E4}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G21">
+    <sortCondition ref="D1:D21"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{219C8427-6CA8-4AC2-8AE0-821699F20E16}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{8E5C6029-6FCB-4B94-93E4-4C3C34A9F7C5}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{E2841EB3-5084-4929-A439-0A23EE544718}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{6BCAB224-BD40-499B-A620-D2DC94BCB86A}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{C8747F23-FDB3-4BA6-8575-D197D5B1C93E}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{DB2BBF42-F518-4A1E-95CA-38EEA04006F2}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{EDC334DB-3246-41E1-AE44-33161B2E2DD7}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{4626443E-6DE0-4275-8A7F-9D7124713A02}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{856C650E-CC58-4970-852E-191709AD2BD1}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{A182A3BD-C238-4C10-B093-B05CE18A186E}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{D3E9D72F-C3F8-49F6-9C0E-41C297013BC1}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{02814467-3A77-4D7D-A3AF-48EC497A1821}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{C1106133-D595-48A6-919E-B146B882F42A}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{4D31214C-32C1-44B3-AEC5-D42C7B8FBA3B}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -559,15 +568,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75A7CC99-7169-4760-9207-6C67A51C3FF7}">
-  <dimension ref="A1:G20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D4E153E-8F2F-4D62-8670-7DC9B526FA81}">
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="49.140625" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" customWidth="1"/>
   </cols>
@@ -600,19 +609,19 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -620,19 +629,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -640,19 +649,19 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -660,19 +669,19 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -680,19 +689,19 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -700,19 +709,19 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -720,19 +729,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -740,19 +749,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -760,19 +769,19 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -780,19 +789,19 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -800,19 +809,19 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -820,19 +829,19 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -840,19 +849,19 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="F14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -860,19 +869,19 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -880,19 +889,19 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F16" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -900,19 +909,19 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E17" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F17" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -920,19 +929,19 @@
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -940,19 +949,19 @@
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="F19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -960,19 +969,39 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="E20" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G20" t="s">
-        <v>39</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/Bibsam_tidskriftslistor/scifree_data_markallen.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_markallen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06569E38-7459-49AA-8774-1B06A3D93D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{207CB56B-4B0A-447E-BF38-D4895766EC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="79">
   <si>
     <t>ISSN Electronic</t>
   </si>
@@ -79,9 +79,6 @@
     <t>British Journal of Healthcare Management</t>
   </si>
   <si>
-    <t>British Journal of Hospital Medicine</t>
-  </si>
-  <si>
     <t>International Journal of Therapy &amp; Rehabilitation</t>
   </si>
   <si>
@@ -124,9 +121,6 @@
     <t>1759-7382</t>
   </si>
   <si>
-    <t>1759-7390</t>
-  </si>
-  <si>
     <t>1759-779X</t>
   </si>
   <si>
@@ -169,9 +163,6 @@
     <t>https://www.magonlinelibrary.com/journal/bjom</t>
   </si>
   <si>
-    <t>https://www.magonlinelibrary.com/journal/hmed</t>
-  </si>
-  <si>
     <t>https://www.magonlinelibrary.com/journal/bjhc</t>
   </si>
   <si>
@@ -199,9 +190,6 @@
     <t>https://www.magonlinelibrary.com/journal/ijap</t>
   </si>
   <si>
-    <t>Open</t>
-  </si>
-  <si>
     <t>Journal of Prescribing Practice</t>
   </si>
   <si>
@@ -233,6 +221,42 @@
   </si>
   <si>
     <t>https://www.magonlinelibrary.com/journal/llwc</t>
+  </si>
+  <si>
+    <t>2978-8250</t>
+  </si>
+  <si>
+    <t>Transplant and Transfusion</t>
+  </si>
+  <si>
+    <t>https://www.magonlinelibrary.com/journal/trtr</t>
+  </si>
+  <si>
+    <t>2978-8269</t>
+  </si>
+  <si>
+    <t>Women's Health in Primary Care</t>
+  </si>
+  <si>
+    <t>https://www.magonlinelibrary.com/journal/whpc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2978-8277  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Perioperative Care </t>
+  </si>
+  <si>
+    <t>https://www.magonlinelibrary.com/journal/jpoc</t>
+  </si>
+  <si>
+    <t>2978-8242</t>
+  </si>
+  <si>
+    <t>Simulation in Healthcare Education</t>
+  </si>
+  <si>
+    <t>https://www.magonlinelibrary.com/journal/sihe</t>
   </si>
 </sst>
 </file>
@@ -288,19 +312,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{49E04D57-5B6F-47EC-961C-ED099BD000E4}" name="Table2" displayName="Table2" ref="A1:G21" totalsRowShown="0">
-  <autoFilter ref="A1:G21" xr:uid="{49E04D57-5B6F-47EC-961C-ED099BD000E4}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G21">
-    <sortCondition ref="D1:D21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5E22FD01-4634-4DBC-BC6E-93C563E5EFDB}" name="Table1" displayName="Table1" ref="A1:G24" totalsRowShown="0">
+  <autoFilter ref="A1:G24" xr:uid="{5E22FD01-4634-4DBC-BC6E-93C563E5EFDB}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G24">
+    <sortCondition ref="D1:D24"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{4626443E-6DE0-4275-8A7F-9D7124713A02}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{856C650E-CC58-4970-852E-191709AD2BD1}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{A182A3BD-C238-4C10-B093-B05CE18A186E}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{D3E9D72F-C3F8-49F6-9C0E-41C297013BC1}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{02814467-3A77-4D7D-A3AF-48EC497A1821}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{C1106133-D595-48A6-919E-B146B882F42A}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{4D31214C-32C1-44B3-AEC5-D42C7B8FBA3B}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{013F4365-E2C3-41F1-9E53-890C482C16F2}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{95ED6576-57C5-4B64-A012-21AE37948FC1}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{39C15E96-66B6-4F45-9D9B-18DF083DE53D}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{45CE7E0F-0E98-4C92-ABB0-89C9D41502E2}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{ADAAA329-AA21-482D-8979-1A9D368BDDED}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{D7C2434A-EDFE-4EA5-B131-7FAE8AB3B297}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{89FAC30A-F06B-4DDA-94F4-EC37D719AE70}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -568,14 +592,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D4E153E-8F2F-4D62-8670-7DC9B526FA81}">
-  <dimension ref="A1:G21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FA3705D-E9C4-4E34-94D6-BF8A861CFD60}">
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="52" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" customWidth="1"/>
@@ -609,19 +633,19 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -629,19 +653,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -649,19 +673,19 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -669,19 +693,19 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -689,19 +713,19 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -709,19 +733,19 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -729,19 +753,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -752,16 +776,16 @@
         <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -769,19 +793,19 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -789,19 +813,19 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -809,19 +833,19 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -829,19 +853,19 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -849,19 +873,19 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -869,19 +893,19 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -889,19 +913,19 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -909,19 +933,19 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -929,19 +953,19 @@
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="E18" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="F18" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -949,19 +973,19 @@
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -969,19 +993,19 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="E20" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="F20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -989,19 +1013,79 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F21" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G21" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" t="s">
+        <v>36</v>
+      </c>
+      <c r="G23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" t="s">
+        <v>72</v>
+      </c>
+      <c r="F24" t="s">
+        <v>36</v>
+      </c>
+      <c r="G24" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
